--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -526,6 +526,9 @@
       <c r="C11" t="str">
         <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -584,7 +587,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520100</v>
+        <v>0105401052015201020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -530,9 +530,90 @@
         <v>20</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>859_喷色小米果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -587,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105401052015201020</v>
+        <v>01054010520152010201010525103010550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -610,6 +610,9 @@
       <c r="C21" t="str">
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -668,7 +671,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01054010520152010201010525103010550</v>
+        <v>010540105201520102010105251030105511</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -614,9 +614,92 @@
         <v>11</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>155_曼塔_Menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>479_绿灵草_lepidium_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -671,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520102010105251030105511</v>
+        <v>01054010520152010201010525103010551110821031016810</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -696,6 +696,9 @@
       <c r="C31" t="str">
         <v>479_绿灵草_lepidium_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -754,7 +757,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01054010520152010201010525103010551110821031016810</v>
+        <v>010540105201520102010105251030105511108210310168110</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -700,9 +700,95 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>5</v>
+      </c>
+      <c r="C32" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v/>
+      </c>
+      <c r="C36" t="str">
+        <v>604_康乃馨粉佳人_pink_undefined_20stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>602_康乃馨白_white_undefined_20stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>6</v>
+      </c>
+      <c r="C38" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -757,7 +843,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520102010105251030105511108210310168110</v>
+        <v>010540105201520102010105251030105511108210310168110118101101561050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -783,7 +783,7 @@
     </row>
     <row r="41">
       <c r="C41" t="str">
-        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+        <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -785,6 +785,9 @@
       <c r="C41" t="str">
         <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -843,7 +846,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520102010105251030105511108210310168110118101101561050</v>
+        <v>010540105201520102010105251030105511108210310168110118101101561055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -789,9 +789,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>7</v>
+      </c>
+      <c r="C44" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>415_百子莲_Agapanthus_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -846,7 +926,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520102010105251030105511108210310168110118101101561055</v>
+        <v>010540105201520102010105251030105511108210310168110118101101561055530351156105150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -868,6 +868,9 @@
       <c r="C51" t="str">
         <v>623_多丁粉太子_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -926,7 +929,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010540105201520102010105251030105511108210310168110118101101561055530351156105150</v>
+        <v>0105401052015201020101052510301055111082103101681101181011015610555303511561051510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-6-2.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -872,9 +872,83 @@
         <v>10</v>
       </c>
     </row>
+    <row r="52" xml:space="preserve">
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>8</v>
+      </c>
+      <c r="C53" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>9</v>
+      </c>
+      <c r="C58" t="str">
+        <v>646_芍药莎拉_Sarah_undefined_5stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>11</v>
+      </c>
+      <c r="C59" t="str">
+        <v>314_松虫草花边黑_scabiosa_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L59"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -929,7 +1003,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105401052015201020101052510301055111082103101681101181011015610555303511561051510</v>
+        <v>01054010520152010201010525103010551110821031016811011810110156105553035115610515105102010101020015</v>
       </c>
     </row>
   </sheetData>
